--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9381,0.0161,0.0242,0.0004</t>
-  </si>
-  <si>
-    <t>0.8397,0.0013,0.0056,0.0593</t>
-  </si>
-  <si>
-    <t>0.9148,0.0216,0.0235,0.0026</t>
-  </si>
-  <si>
-    <t>0.9488,0.0024,0.0096,0.0048</t>
-  </si>
-  <si>
-    <t>0.9788,0.0172,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9914,0.0060,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9932,0.0054,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9920,0.0052,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9874,0.0099,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9756,0.0229,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9868,0.0096,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9953,0.0027,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9133,0.0031,0.1018,0.0002</t>
-  </si>
-  <si>
-    <t>0.5709,0.0026,0.5795,0.0002</t>
-  </si>
-  <si>
-    <t>0.6032,0.0098,0.4809,0.0003</t>
-  </si>
-  <si>
-    <t>0.5294,0.0020,0.6223,0.0003</t>
-  </si>
-  <si>
-    <t>0.8108,0.0081,0.2297,0.0006</t>
-  </si>
-  <si>
-    <t>0.0145,0.9789,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.0300,0.9620,0.0025,0.0004</t>
-  </si>
-  <si>
-    <t>0.2757,0.7327,0.0122,0.0008</t>
-  </si>
-  <si>
-    <t>0.0497,0.9435,0.0025,0.0003</t>
-  </si>
-  <si>
-    <t>0.0026,0.9945,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.7594,0.0014,0.3856,0.0003</t>
-  </si>
-  <si>
-    <t>0.6433,0.0009,0.5362,0.0003</t>
-  </si>
-  <si>
-    <t>0.0520,0.0004,0.9696,0.0001</t>
-  </si>
-  <si>
-    <t>0.5018,0.0014,0.6498,0.0003</t>
-  </si>
-  <si>
-    <t>0.3142,0.0005,0.8316,0.0001</t>
-  </si>
-  <si>
-    <t>0.4026,0.0005,0.7632,0.0002</t>
-  </si>
-  <si>
-    <t>0.0172,0.0001,0.9908,0.0001</t>
-  </si>
-  <si>
-    <t>0.4904,0.3941,0.0292,0.0004</t>
-  </si>
-  <si>
-    <t>0.2774,0.0227,0.7096,0.0015</t>
-  </si>
-  <si>
-    <t>0.0008,0.0003,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0511,0.5670,0.3257,0.0004</t>
-  </si>
-  <si>
-    <t>0.8840,0.0378,0.0454,0.0015</t>
-  </si>
-  <si>
-    <t>0.8389,0.0452,0.0881,0.0006</t>
-  </si>
-  <si>
-    <t>0.5523,0.4921,0.0116,0.0005</t>
-  </si>
-  <si>
-    <t>0.0911,0.8233,0.0554,0.0009</t>
-  </si>
-  <si>
-    <t>0.2249,0.2329,0.2479,0.0003</t>
-  </si>
-  <si>
-    <t>0.1352,0.0088,0.8856,0.0002</t>
-  </si>
-  <si>
-    <t>0.1787,0.0055,0.8530,0.0003</t>
-  </si>
-  <si>
-    <t>0.1202,0.0006,0.9232,0.0002</t>
-  </si>
-  <si>
-    <t>0.0843,0.0047,0.9364,0.0001</t>
-  </si>
-  <si>
-    <t>0.0652,0.6879,0.0970,0.0001</t>
-  </si>
-  <si>
-    <t>0.0272,0.0006,0.9816,0.0001</t>
-  </si>
-  <si>
-    <t>0.9192,0.0217,0.0205,0.0004</t>
-  </si>
-  <si>
-    <t>0.1116,0.8209,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.0488,0.8981,0.0222,0.0004</t>
-  </si>
-  <si>
-    <t>0.3069,0.4636,0.0493,0.0008</t>
-  </si>
-  <si>
-    <t>0.0023,0.0006,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0003,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0889,0.0007,0.9474,0.0001</t>
-  </si>
-  <si>
-    <t>0.7496,0.0004,0.4484,0.0001</t>
-  </si>
-  <si>
-    <t>0.0143,0.0007,0.9918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0181,0.0012,0.9879,0.0000</t>
-  </si>
-  <si>
-    <t>0.9356,0.0732,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.9570,0.0225,0.0120,0.0004</t>
-  </si>
-  <si>
-    <t>0.9172,0.0760,0.0082,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.0007,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.9705,0.0199,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.9707,0.0220,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.5648,0.4877,0.0175,0.0008</t>
-  </si>
-  <si>
-    <t>0.0012,0.1896,0.9861,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0266,0.0009,0.9831,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.6817,0.9492,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0002,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.1558,0.7692,0.0258,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9986,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.5203,0.0092,0.5533,0.0009</t>
-  </si>
-  <si>
-    <t>0.8409,0.0227,0.1217,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0019,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.5067,0.9838,0.0000</t>
-  </si>
-  <si>
-    <t>0.0086,0.4526,0.8380,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9854,0.0959,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.6424,0.9210,0.0000</t>
-  </si>
-  <si>
-    <t>0.9347,0.0008,0.0172,0.0059</t>
-  </si>
-  <si>
-    <t>0.3951,0.0013,0.0037,0.6189</t>
-  </si>
-  <si>
-    <t>0.8215,0.0002,0.0012,0.1425</t>
-  </si>
-  <si>
-    <t>0.9361,0.0003,0.0093,0.0094</t>
-  </si>
-  <si>
-    <t>0.9421,0.0011,0.0125,0.0054</t>
-  </si>
-  <si>
-    <t>0.8812,0.0018,0.0135,0.0183</t>
-  </si>
-  <si>
-    <t>0.0035,0.5197,0.8875,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.1663,0.9762,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.5215,0.9390,0.0000</t>
-  </si>
-  <si>
-    <t>0.0058,0.4063,0.8881,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.7351,0.8791,0.0000</t>
-  </si>
-  <si>
-    <t>0.0107,0.1251,0.9283,0.0000</t>
-  </si>
-  <si>
-    <t>0.9740,0.0245,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9771,0.0214,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9602,0.0483,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9840,0.0103,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9657,0.0269,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9711,0.0250,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.9661,0.0260,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9506,0.0558,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0011,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9826,0.0147,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0047,0.0003,0.0001</t>
+    <t>0.9394,0.0060,0.0418,0.0004</t>
+  </si>
+  <si>
+    <t>0.8622,0.0035,0.0089,0.0312</t>
+  </si>
+  <si>
+    <t>0.9783,0.0053,0.0044,0.0006</t>
+  </si>
+  <si>
+    <t>0.8859,0.0023,0.0206,0.0174</t>
+  </si>
+  <si>
+    <t>0.9801,0.0146,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9885,0.0066,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9760,0.0261,0.0015,0.0001</t>
   </si>
   <si>
     <t>0.9950,0.0029,0.0003,0.0001</t>
   </si>
   <si>
-    <t>0.9837,0.0114,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9657,0.0355,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9705,0.0247,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9968,0.0017,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.1303,0.0007,0.9235,0.0001</t>
-  </si>
-  <si>
-    <t>0.9179,0.0044,0.0818,0.0002</t>
-  </si>
-  <si>
-    <t>0.0610,0.0013,0.9591,0.0001</t>
-  </si>
-  <si>
-    <t>0.0124,0.9793,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.0191,0.9695,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.0645,0.9355,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.0576,0.9339,0.0042,0.0006</t>
-  </si>
-  <si>
-    <t>0.0199,0.9711,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.0070,0.9866,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.4344,0.5885,0.0171,0.0006</t>
-  </si>
-  <si>
-    <t>0.8293,0.0107,0.1816,0.0003</t>
-  </si>
-  <si>
-    <t>0.4655,0.0009,0.6882,0.0003</t>
-  </si>
-  <si>
-    <t>0.9053,0.0051,0.0964,0.0002</t>
-  </si>
-  <si>
-    <t>0.7843,0.0063,0.2805,0.0006</t>
-  </si>
-  <si>
-    <t>0.7133,0.0988,0.0659,0.0096</t>
-  </si>
-  <si>
-    <t>0.0017,0.9954,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.9973,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.5766,0.1435,0.1154,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9560,0.9090,0.0000</t>
-  </si>
-  <si>
-    <t>0.0312,0.9534,0.0086,0.0002</t>
-  </si>
-  <si>
-    <t>0.5814,0.4995,0.0099,0.0002</t>
-  </si>
-  <si>
-    <t>0.5371,0.5019,0.0149,0.0007</t>
-  </si>
-  <si>
-    <t>0.9749,0.0187,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9774,0.0142,0.0035,0.0003</t>
-  </si>
-  <si>
-    <t>0.9515,0.0435,0.0038,0.0005</t>
-  </si>
-  <si>
-    <t>0.9708,0.0220,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.9922,0.0041,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9525,0.0330,0.0116,0.0004</t>
-  </si>
-  <si>
-    <t>0.9821,0.0110,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9869,0.0083,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.0094,0.1377,0.9352,0.0000</t>
-  </si>
-  <si>
-    <t>0.0432,0.0974,0.8149,0.0001</t>
-  </si>
-  <si>
-    <t>0.0768,0.0068,0.9263,0.0001</t>
-  </si>
-  <si>
-    <t>0.1190,0.0064,0.9026,0.0001</t>
-  </si>
-  <si>
-    <t>0.8965,0.0101,0.0789,0.0002</t>
-  </si>
-  <si>
-    <t>0.6035,0.0055,0.5126,0.0005</t>
-  </si>
-  <si>
-    <t>0.7615,0.0006,0.4298,0.0001</t>
-  </si>
-  <si>
-    <t>0.8833,0.0093,0.1003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9779,0.0003,0.0028,0.0027</t>
-  </si>
-  <si>
-    <t>0.0261,0.0006,0.0018,0.9840</t>
-  </si>
-  <si>
-    <t>0.0954,0.0032,0.0039,0.9306</t>
-  </si>
-  <si>
-    <t>0.6233,0.0001,0.0055,0.3254</t>
-  </si>
-  <si>
-    <t>0.0015,0.6751,0.8993,0.0000</t>
-  </si>
-  <si>
-    <t>0.9681,0.0227,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.2894,0.6986,0.0195,0.0016</t>
-  </si>
-  <si>
-    <t>0.9887,0.0049,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.6393,0.3692,0.0205,0.0004</t>
-  </si>
-  <si>
-    <t>0.9807,0.0063,0.0051,0.0005</t>
-  </si>
-  <si>
-    <t>0.9342,0.0015,0.0077,0.0093</t>
-  </si>
-  <si>
-    <t>0.9874,0.0056,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0029,0.9972,0.0006</t>
-  </si>
-  <si>
-    <t>0.9765,0.0026,0.0080,0.0006</t>
-  </si>
-  <si>
-    <t>0.9774,0.0050,0.0074,0.0006</t>
-  </si>
-  <si>
-    <t>0.7012,0.0917,0.1258,0.0003</t>
-  </si>
-  <si>
-    <t>0.9271,0.0234,0.0199,0.0006</t>
-  </si>
-  <si>
-    <t>0.8888,0.0384,0.0378,0.0010</t>
-  </si>
-  <si>
-    <t>0.7849,0.0510,0.1032,0.0005</t>
-  </si>
-  <si>
-    <t>0.8430,0.0436,0.0776,0.0004</t>
-  </si>
-  <si>
-    <t>0.8913,0.0519,0.0207,0.0007</t>
-  </si>
-  <si>
-    <t>0.9907,0.0057,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9910,0.0046,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9837,0.0102,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9933,0.0027,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9834,0.0092,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9828,0.0121,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9843,0.0103,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9881,0.0064,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.5623,0.5130,0.0084,0.0004</t>
-  </si>
-  <si>
-    <t>0.7436,0.2963,0.0114,0.0002</t>
-  </si>
-  <si>
-    <t>0.5997,0.3558,0.0303,0.0006</t>
-  </si>
-  <si>
-    <t>0.9398,0.0358,0.0109,0.0009</t>
-  </si>
-  <si>
-    <t>0.8979,0.0985,0.0048,0.0005</t>
-  </si>
-  <si>
-    <t>0.8531,0.0940,0.0331,0.0012</t>
-  </si>
-  <si>
-    <t>0.9444,0.0436,0.0072,0.0003</t>
-  </si>
-  <si>
-    <t>0.8379,0.1243,0.0345,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8747,0.0978,0.0223,0.0008</t>
-  </si>
-  <si>
-    <t>0.0033,0.0004,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0326,0.0032,0.9724,0.0001</t>
-  </si>
-  <si>
-    <t>0.0612,0.0010,0.9616,0.0001</t>
-  </si>
-  <si>
-    <t>0.0062,0.0026,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0191,0.0004,0.9877,0.0000</t>
-  </si>
-  <si>
-    <t>0.0196,0.0004,0.9887,0.0000</t>
-  </si>
-  <si>
-    <t>0.0181,0.0003,0.9884,0.0001</t>
-  </si>
-  <si>
-    <t>0.4951,0.0074,0.5958,0.0005</t>
-  </si>
-  <si>
-    <t>0.2075,0.0049,0.8396,0.0004</t>
-  </si>
-  <si>
-    <t>0.8613,0.0117,0.1232,0.0003</t>
-  </si>
-  <si>
-    <t>0.7486,0.0071,0.3275,0.0002</t>
-  </si>
-  <si>
-    <t>0.5424,0.0254,0.4333,0.0003</t>
-  </si>
-  <si>
-    <t>0.8255,0.0057,0.2316,0.0002</t>
-  </si>
-  <si>
-    <t>0.8074,0.0087,0.2285,0.0008</t>
-  </si>
-  <si>
-    <t>0.7420,0.0182,0.2598,0.0007</t>
-  </si>
-  <si>
-    <t>0.3031,0.7190,0.0145,0.0005</t>
-  </si>
-  <si>
-    <t>0.1299,0.8715,0.0073,0.0003</t>
-  </si>
-  <si>
-    <t>0.4145,0.6349,0.0161,0.0006</t>
-  </si>
-  <si>
-    <t>0.3546,0.6776,0.0099,0.0018</t>
-  </si>
-  <si>
-    <t>0.0996,0.8958,0.0050,0.0014</t>
-  </si>
-  <si>
-    <t>0.8836,0.0057,0.1263,0.0003</t>
-  </si>
-  <si>
-    <t>0.8430,0.0022,0.2024,0.0006</t>
-  </si>
-  <si>
-    <t>0.8772,0.0028,0.1523,0.0004</t>
-  </si>
-  <si>
-    <t>0.8200,0.0107,0.2036,0.0003</t>
-  </si>
-  <si>
-    <t>0.8078,0.0032,0.2936,0.0002</t>
-  </si>
-  <si>
-    <t>0.2077,0.0009,0.8705,0.0003</t>
-  </si>
-  <si>
-    <t>0.0332,0.0129,0.9538,0.0003</t>
-  </si>
-  <si>
-    <t>0.0949,0.0163,0.8923,0.0004</t>
-  </si>
-  <si>
-    <t>0.1000,0.0008,0.9460,0.0001</t>
-  </si>
-  <si>
-    <t>0.0714,0.0502,0.8635,0.0005</t>
-  </si>
-  <si>
-    <t>0.9854,0.0093,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9878,0.0086,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9618,0.0327,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.9560,0.0453,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.9856,0.0112,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9724,0.0223,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.9375,0.0584,0.0067,0.0004</t>
-  </si>
-  <si>
-    <t>0.9928,0.0045,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0382,0.0017,0.9628,0.0012</t>
-  </si>
-  <si>
-    <t>0.7673,0.0788,0.1155,0.0017</t>
-  </si>
-  <si>
-    <t>0.8335,0.0222,0.1359,0.0009</t>
-  </si>
-  <si>
-    <t>0.0249,0.0008,0.9870,0.0000</t>
-  </si>
-  <si>
-    <t>0.0107,0.0008,0.9951,0.0000</t>
-  </si>
-  <si>
-    <t>0.0439,0.0058,0.9624,0.0001</t>
+    <t>0.9865,0.0103,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9669,0.0324,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9934,0.0043,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0025,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8019,0.0032,0.2912,0.0003</t>
+  </si>
+  <si>
+    <t>0.4369,0.0032,0.6896,0.0002</t>
+  </si>
+  <si>
+    <t>0.7290,0.0019,0.4379,0.0001</t>
+  </si>
+  <si>
+    <t>0.5779,0.0007,0.5982,0.0002</t>
+  </si>
+  <si>
+    <t>0.6908,0.0240,0.2977,0.0009</t>
+  </si>
+  <si>
+    <t>0.0059,0.9895,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0582,0.9336,0.0043,0.0002</t>
+  </si>
+  <si>
+    <t>0.2105,0.7874,0.0158,0.0008</t>
+  </si>
+  <si>
+    <t>0.0890,0.9053,0.0039,0.0003</t>
+  </si>
+  <si>
+    <t>0.0082,0.9873,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.8516,0.0027,0.2056,0.0004</t>
+  </si>
+  <si>
+    <t>0.6751,0.0012,0.4969,0.0003</t>
+  </si>
+  <si>
+    <t>0.0487,0.0006,0.9690,0.0001</t>
+  </si>
+  <si>
+    <t>0.5565,0.0021,0.5855,0.0005</t>
+  </si>
+  <si>
+    <t>0.0381,0.0008,0.9760,0.0001</t>
+  </si>
+  <si>
+    <t>0.1883,0.0003,0.9051,0.0001</t>
+  </si>
+  <si>
+    <t>0.0225,0.0002,0.9896,0.0000</t>
+  </si>
+  <si>
+    <t>0.4325,0.4276,0.0357,0.0005</t>
+  </si>
+  <si>
+    <t>0.7112,0.0762,0.1674,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0983,0.8103,0.0368,0.0004</t>
+  </si>
+  <si>
+    <t>0.9222,0.0320,0.0226,0.0005</t>
+  </si>
+  <si>
+    <t>0.9020,0.0391,0.0345,0.0002</t>
+  </si>
+  <si>
+    <t>0.5051,0.5262,0.0146,0.0009</t>
+  </si>
+  <si>
+    <t>0.1953,0.7127,0.0547,0.0015</t>
+  </si>
+  <si>
+    <t>0.1809,0.2145,0.3594,0.0006</t>
+  </si>
+  <si>
+    <t>0.2504,0.0026,0.8394,0.0002</t>
+  </si>
+  <si>
+    <t>0.1975,0.0095,0.8279,0.0005</t>
+  </si>
+  <si>
+    <t>0.3827,0.0025,0.7484,0.0003</t>
+  </si>
+  <si>
+    <t>0.0646,0.0653,0.8644,0.0001</t>
+  </si>
+  <si>
+    <t>0.0458,0.8335,0.0550,0.0001</t>
+  </si>
+  <si>
+    <t>0.0042,0.0007,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.8742,0.0441,0.0240,0.0011</t>
+  </si>
+  <si>
+    <t>0.0176,0.9686,0.0015,0.0022</t>
+  </si>
+  <si>
+    <t>0.0560,0.8546,0.0420,0.0004</t>
+  </si>
+  <si>
+    <t>0.0736,0.8939,0.0092,0.0007</t>
+  </si>
+  <si>
+    <t>0.0014,0.0010,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0003,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0790,0.0007,0.9452,0.0002</t>
+  </si>
+  <si>
+    <t>0.3721,0.0003,0.8035,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.0003,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0739,0.0027,0.9493,0.0001</t>
+  </si>
+  <si>
+    <t>0.9283,0.0731,0.0066,0.0003</t>
+  </si>
+  <si>
+    <t>0.9587,0.0264,0.0082,0.0005</t>
+  </si>
+  <si>
+    <t>0.8850,0.1172,0.0071,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0011,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.9876,0.0074,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9614,0.0325,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.7195,0.3259,0.0114,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.1642,0.9940,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0480,0.0010,0.9695,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.3328,0.9724,0.0000</t>
   </si>
   <si>
     <t>0.0008,0.0002,0.9996,0.0000</t>
   </si>
   <si>
-    <t>0.1111,0.0006,0.9321,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0575,0.0079,0.9408,0.0002</t>
-  </si>
-  <si>
-    <t>0.2138,0.0040,0.8354,0.0004</t>
-  </si>
-  <si>
-    <t>0.6459,0.0016,0.4767,0.0008</t>
-  </si>
-  <si>
-    <t>0.7437,0.0017,0.4082,0.0002</t>
-  </si>
-  <si>
-    <t>0.9494,0.0024,0.0452,0.0001</t>
-  </si>
-  <si>
-    <t>0.9414,0.0482,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.9554,0.0477,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.9886,0.0085,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9768,0.0192,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.9833,0.0096,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9302,0.0745,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.9572,0.0401,0.0025,0.0003</t>
-  </si>
-  <si>
-    <t>0.9525,0.0314,0.0031,0.0014</t>
-  </si>
-  <si>
-    <t>0.2733,0.0064,0.7794,0.0003</t>
-  </si>
-  <si>
-    <t>0.0941,0.0067,0.9171,0.0002</t>
-  </si>
-  <si>
-    <t>0.1030,0.0609,0.7722,0.0003</t>
-  </si>
-  <si>
-    <t>0.4892,0.0082,0.5916,0.0005</t>
-  </si>
-  <si>
-    <t>0.0282,0.0007,0.9841,0.0000</t>
-  </si>
-  <si>
-    <t>0.2484,0.0006,0.8369,0.0005</t>
-  </si>
-  <si>
-    <t>0.3318,0.0025,0.7820,0.0002</t>
-  </si>
-  <si>
-    <t>0.1108,0.0006,0.9376,0.0001</t>
-  </si>
-  <si>
-    <t>0.9660,0.0063,0.0122,0.0007</t>
-  </si>
-  <si>
-    <t>0.8929,0.0052,0.0211,0.0102</t>
-  </si>
-  <si>
-    <t>0.9795,0.0004,0.0022,0.0023</t>
-  </si>
-  <si>
-    <t>0.7195,0.0002,0.0025,0.2951</t>
-  </si>
-  <si>
-    <t>0.0986,0.0005,0.0017,0.9496</t>
-  </si>
-  <si>
-    <t>0.9528,0.0036,0.0295,0.0003</t>
+    <t>0.1169,0.7721,0.0424,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.5933,0.0093,0.4691,0.0015</t>
+  </si>
+  <si>
+    <t>0.6898,0.0216,0.3111,0.0007</t>
+  </si>
+  <si>
+    <t>0.0041,0.0025,0.9962,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.5031,0.9829,0.0000</t>
+  </si>
+  <si>
+    <t>0.0181,0.1191,0.9128,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9850,0.1066,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.8097,0.8390,0.0000</t>
+  </si>
+  <si>
+    <t>0.7175,0.0014,0.1416,0.0263</t>
+  </si>
+  <si>
+    <t>0.3544,0.0003,0.0015,0.7434</t>
+  </si>
+  <si>
+    <t>0.8935,0.0006,0.0054,0.0286</t>
+  </si>
+  <si>
+    <t>0.8701,0.0003,0.0113,0.0356</t>
+  </si>
+  <si>
+    <t>0.9373,0.0009,0.0172,0.0060</t>
+  </si>
+  <si>
+    <t>0.8738,0.0006,0.0058,0.0325</t>
+  </si>
+  <si>
+    <t>0.0041,0.7823,0.7049,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.4812,0.9455,0.0000</t>
+  </si>
+  <si>
+    <t>0.0078,0.2362,0.9276,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.1335,0.9808,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.4480,0.9789,0.0000</t>
+  </si>
+  <si>
+    <t>0.1119,0.1666,0.5180,0.0001</t>
+  </si>
+  <si>
+    <t>0.9868,0.0100,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9834,0.0139,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9664,0.0380,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9671,0.0180,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.9214,0.0785,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9851,0.0102,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9700,0.0264,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.9575,0.0512,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0017,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9910,0.0059,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9903,0.0063,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9957,0.0022,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9873,0.0078,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9697,0.0294,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.9781,0.0180,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9946,0.0032,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.1180,0.0006,0.9320,0.0001</t>
+  </si>
+  <si>
+    <t>0.8762,0.0076,0.1284,0.0003</t>
+  </si>
+  <si>
+    <t>0.0776,0.0013,0.9505,0.0001</t>
+  </si>
+  <si>
+    <t>0.0178,0.9720,0.0040,0.0003</t>
+  </si>
+  <si>
+    <t>0.0246,0.9627,0.0058,0.0004</t>
+  </si>
+  <si>
+    <t>0.0208,0.9717,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.0609,0.9306,0.0043,0.0006</t>
+  </si>
+  <si>
+    <t>0.0407,0.9473,0.0043,0.0005</t>
+  </si>
+  <si>
+    <t>0.0037,0.9913,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.4672,0.5475,0.0181,0.0006</t>
+  </si>
+  <si>
+    <t>0.8609,0.0064,0.1622,0.0003</t>
+  </si>
+  <si>
+    <t>0.2860,0.0010,0.8280,0.0001</t>
+  </si>
+  <si>
+    <t>0.9108,0.0035,0.0914,0.0003</t>
+  </si>
+  <si>
+    <t>0.7028,0.0136,0.3506,0.0005</t>
+  </si>
+  <si>
+    <t>0.6528,0.1073,0.0487,0.0218</t>
+  </si>
+  <si>
+    <t>0.0015,0.9949,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.9934,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.4373,0.3544,0.0514,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.9627,0.6360,0.0001</t>
+  </si>
+  <si>
+    <t>0.2242,0.7688,0.0152,0.0002</t>
+  </si>
+  <si>
+    <t>0.4989,0.5945,0.0070,0.0002</t>
+  </si>
+  <si>
+    <t>0.6137,0.4339,0.0131,0.0006</t>
+  </si>
+  <si>
+    <t>0.8943,0.0971,0.0104,0.0004</t>
+  </si>
+  <si>
+    <t>0.9436,0.0416,0.0092,0.0004</t>
+  </si>
+  <si>
+    <t>0.9753,0.0183,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.9814,0.0114,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9926,0.0037,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9692,0.0217,0.0066,0.0003</t>
+  </si>
+  <si>
+    <t>0.9748,0.0205,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.9704,0.0243,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.0292,0.1264,0.8684,0.0001</t>
+  </si>
+  <si>
+    <t>0.0190,0.1397,0.8747,0.0001</t>
+  </si>
+  <si>
+    <t>0.0504,0.0172,0.9334,0.0001</t>
+  </si>
+  <si>
+    <t>0.1560,0.0010,0.9054,0.0001</t>
+  </si>
+  <si>
+    <t>0.9325,0.0048,0.0531,0.0001</t>
+  </si>
+  <si>
+    <t>0.7510,0.0071,0.3335,0.0003</t>
+  </si>
+  <si>
+    <t>0.6899,0.0006,0.5021,0.0002</t>
+  </si>
+  <si>
+    <t>0.8689,0.0116,0.1127,0.0003</t>
+  </si>
+  <si>
+    <t>0.9626,0.0006,0.0039,0.0055</t>
+  </si>
+  <si>
+    <t>0.0070,0.0002,0.0007,0.9960</t>
+  </si>
+  <si>
+    <t>0.4581,0.0014,0.0030,0.5209</t>
+  </si>
+  <si>
+    <t>0.7304,0.0003,0.0130,0.1475</t>
+  </si>
+  <si>
+    <t>0.0012,0.8237,0.7772,0.0000</t>
+  </si>
+  <si>
+    <t>0.9808,0.0133,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.6059,0.3590,0.0220,0.0007</t>
+  </si>
+  <si>
+    <t>0.9686,0.0172,0.0050,0.0003</t>
+  </si>
+  <si>
+    <t>0.4464,0.6108,0.0149,0.0003</t>
+  </si>
+  <si>
+    <t>0.9798,0.0060,0.0045,0.0006</t>
+  </si>
+  <si>
+    <t>0.8998,0.0025,0.0200,0.0132</t>
+  </si>
+  <si>
+    <t>0.9804,0.0095,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0054,0.9946,0.0014</t>
+  </si>
+  <si>
+    <t>0.9623,0.0036,0.0122,0.0014</t>
+  </si>
+  <si>
+    <t>0.9891,0.0027,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.7473,0.1150,0.0631,0.0002</t>
+  </si>
+  <si>
+    <t>0.9237,0.0275,0.0152,0.0012</t>
+  </si>
+  <si>
+    <t>0.9208,0.0272,0.0280,0.0006</t>
+  </si>
+  <si>
+    <t>0.8160,0.0322,0.1128,0.0004</t>
+  </si>
+  <si>
+    <t>0.8932,0.0278,0.0460,0.0004</t>
+  </si>
+  <si>
+    <t>0.8543,0.0372,0.0617,0.0006</t>
+  </si>
+  <si>
+    <t>0.9868,0.0084,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9946,0.0032,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9663,0.0236,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.9892,0.0047,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9891,0.0067,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9820,0.0147,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9868,0.0078,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9816,0.0121,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.6401,0.4200,0.0099,0.0004</t>
+  </si>
+  <si>
+    <t>0.6919,0.3322,0.0127,0.0002</t>
+  </si>
+  <si>
+    <t>0.6512,0.3222,0.0244,0.0004</t>
+  </si>
+  <si>
+    <t>0.1714,0.0157,0.8168,0.0033</t>
+  </si>
+  <si>
+    <t>0.8604,0.1522,0.0067,0.0003</t>
+  </si>
+  <si>
+    <t>0.9198,0.0554,0.0099,0.0006</t>
+  </si>
+  <si>
+    <t>0.8681,0.1322,0.0106,0.0005</t>
+  </si>
+  <si>
+    <t>0.6682,0.3359,0.0210,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.0019,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.8526,0.1108,0.0237,0.0015</t>
+  </si>
+  <si>
+    <t>0.0017,0.0005,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0080,0.0047,0.9919,0.0000</t>
+  </si>
+  <si>
+    <t>0.2012,0.0009,0.8728,0.0002</t>
+  </si>
+  <si>
+    <t>0.0072,0.0014,0.9948,0.0000</t>
+  </si>
+  <si>
+    <t>0.0167,0.0007,0.9875,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.0002,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0070,0.0003,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.6560,0.0071,0.4409,0.0005</t>
+  </si>
+  <si>
+    <t>0.3494,0.0083,0.6980,0.0010</t>
+  </si>
+  <si>
+    <t>0.8364,0.0136,0.1544,0.0004</t>
+  </si>
+  <si>
+    <t>0.8066,0.0131,0.1920,0.0003</t>
+  </si>
+  <si>
+    <t>0.7207,0.0217,0.2473,0.0003</t>
+  </si>
+  <si>
+    <t>0.7522,0.0040,0.3533,0.0003</t>
+  </si>
+  <si>
+    <t>0.8719,0.0030,0.1640,0.0004</t>
+  </si>
+  <si>
+    <t>0.8215,0.0076,0.2189,0.0005</t>
+  </si>
+  <si>
+    <t>0.3142,0.7121,0.0134,0.0007</t>
+  </si>
+  <si>
+    <t>0.0681,0.9237,0.0057,0.0005</t>
+  </si>
+  <si>
+    <t>0.5733,0.4884,0.0187,0.0005</t>
+  </si>
+  <si>
+    <t>0.3684,0.6752,0.0054,0.0013</t>
+  </si>
+  <si>
+    <t>0.0760,0.9156,0.0036,0.0019</t>
+  </si>
+  <si>
+    <t>0.8836,0.0054,0.1321,0.0002</t>
+  </si>
+  <si>
+    <t>0.8840,0.0022,0.1579,0.0003</t>
+  </si>
+  <si>
+    <t>0.8900,0.0030,0.1193,0.0005</t>
+  </si>
+  <si>
+    <t>0.8425,0.0036,0.2249,0.0003</t>
+  </si>
+  <si>
+    <t>0.8274,0.0034,0.2454,0.0003</t>
+  </si>
+  <si>
+    <t>0.0596,0.0007,0.9639,0.0002</t>
+  </si>
+  <si>
+    <t>0.1292,0.0045,0.8981,0.0003</t>
+  </si>
+  <si>
+    <t>0.2481,0.0337,0.7026,0.0012</t>
+  </si>
+  <si>
+    <t>0.1261,0.0006,0.9340,0.0001</t>
+  </si>
+  <si>
+    <t>0.1396,0.0071,0.8777,0.0003</t>
+  </si>
+  <si>
+    <t>0.9841,0.0113,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9487,0.0494,0.0047,0.0004</t>
+  </si>
+  <si>
+    <t>0.9630,0.0317,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.9559,0.0456,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.9539,0.0359,0.0028,0.0006</t>
+  </si>
+  <si>
+    <t>0.9804,0.0142,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9463,0.0411,0.0066,0.0007</t>
+  </si>
+  <si>
+    <t>0.9901,0.0072,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0606,0.0023,0.9491,0.0011</t>
+  </si>
+  <si>
+    <t>0.4805,0.0203,0.5285,0.0016</t>
+  </si>
+  <si>
+    <t>0.8691,0.0447,0.0566,0.0014</t>
+  </si>
+  <si>
+    <t>0.0247,0.0003,0.9903,0.0000</t>
+  </si>
+  <si>
+    <t>0.0229,0.0056,0.9803,0.0000</t>
+  </si>
+  <si>
+    <t>0.2129,0.0025,0.8654,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.4610,0.0026,0.6623,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0742,0.0076,0.9306,0.0002</t>
+  </si>
+  <si>
+    <t>0.0148,0.0025,0.9872,0.0001</t>
+  </si>
+  <si>
+    <t>0.8115,0.0012,0.2566,0.0006</t>
+  </si>
+  <si>
+    <t>0.8351,0.0034,0.2494,0.0002</t>
+  </si>
+  <si>
+    <t>0.9375,0.0020,0.0779,0.0001</t>
+  </si>
+  <si>
+    <t>0.9462,0.0424,0.0031,0.0007</t>
+  </si>
+  <si>
+    <t>0.9704,0.0227,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.9917,0.0058,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9544,0.0413,0.0050,0.0005</t>
+  </si>
+  <si>
+    <t>0.8985,0.0779,0.0049,0.0017</t>
+  </si>
+  <si>
+    <t>0.9323,0.0791,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.9744,0.0202,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9510,0.0401,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.3256,0.0028,0.7642,0.0003</t>
+  </si>
+  <si>
+    <t>0.0090,0.0049,0.9910,0.0000</t>
+  </si>
+  <si>
+    <t>0.0263,0.0220,0.9592,0.0001</t>
+  </si>
+  <si>
+    <t>0.5873,0.0176,0.4401,0.0004</t>
+  </si>
+  <si>
+    <t>0.0084,0.0004,0.9951,0.0000</t>
+  </si>
+  <si>
+    <t>0.5130,0.0017,0.6153,0.0007</t>
+  </si>
+  <si>
+    <t>0.5978,0.0015,0.5697,0.0003</t>
+  </si>
+  <si>
+    <t>0.1382,0.0013,0.8968,0.0005</t>
+  </si>
+  <si>
+    <t>0.9793,0.0028,0.0069,0.0006</t>
+  </si>
+  <si>
+    <t>0.8419,0.0032,0.0085,0.0376</t>
+  </si>
+  <si>
+    <t>0.9815,0.0005,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.5900,0.0002,0.0121,0.3325</t>
+  </si>
+  <si>
+    <t>0.1112,0.0003,0.0013,0.9477</t>
+  </si>
+  <si>
+    <t>0.9354,0.0048,0.0459,0.0005</t>
   </si>
 </sst>
 </file>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2905,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3689,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
         <v>388</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3899,7 +3899,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
         <v>403</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4347,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
         <v>435</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9394,0.0060,0.0418,0.0004</t>
-  </si>
-  <si>
-    <t>0.8622,0.0035,0.0089,0.0312</t>
-  </si>
-  <si>
-    <t>0.9783,0.0053,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.8859,0.0023,0.0206,0.0174</t>
-  </si>
-  <si>
-    <t>0.9801,0.0146,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9885,0.0066,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9760,0.0261,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0029,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9865,0.0103,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9669,0.0324,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9934,0.0043,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0025,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.8019,0.0032,0.2912,0.0003</t>
-  </si>
-  <si>
-    <t>0.4369,0.0032,0.6896,0.0002</t>
-  </si>
-  <si>
-    <t>0.7290,0.0019,0.4379,0.0001</t>
-  </si>
-  <si>
-    <t>0.5779,0.0007,0.5982,0.0002</t>
-  </si>
-  <si>
-    <t>0.6908,0.0240,0.2977,0.0009</t>
-  </si>
-  <si>
-    <t>0.0059,0.9895,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0582,0.9336,0.0043,0.0002</t>
-  </si>
-  <si>
-    <t>0.2105,0.7874,0.0158,0.0008</t>
-  </si>
-  <si>
-    <t>0.0890,0.9053,0.0039,0.0003</t>
-  </si>
-  <si>
-    <t>0.0082,0.9873,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.8516,0.0027,0.2056,0.0004</t>
-  </si>
-  <si>
-    <t>0.6751,0.0012,0.4969,0.0003</t>
-  </si>
-  <si>
-    <t>0.0487,0.0006,0.9690,0.0001</t>
-  </si>
-  <si>
-    <t>0.5565,0.0021,0.5855,0.0005</t>
-  </si>
-  <si>
-    <t>0.0381,0.0008,0.9760,0.0001</t>
-  </si>
-  <si>
-    <t>0.1883,0.0003,0.9051,0.0001</t>
-  </si>
-  <si>
-    <t>0.0225,0.0002,0.9896,0.0000</t>
-  </si>
-  <si>
-    <t>0.4325,0.4276,0.0357,0.0005</t>
-  </si>
-  <si>
-    <t>0.7112,0.0762,0.1674,0.0008</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0983,0.8103,0.0368,0.0004</t>
-  </si>
-  <si>
-    <t>0.9222,0.0320,0.0226,0.0005</t>
-  </si>
-  <si>
-    <t>0.9020,0.0391,0.0345,0.0002</t>
-  </si>
-  <si>
-    <t>0.5051,0.5262,0.0146,0.0009</t>
-  </si>
-  <si>
-    <t>0.1953,0.7127,0.0547,0.0015</t>
-  </si>
-  <si>
-    <t>0.1809,0.2145,0.3594,0.0006</t>
-  </si>
-  <si>
-    <t>0.2504,0.0026,0.8394,0.0002</t>
-  </si>
-  <si>
-    <t>0.1975,0.0095,0.8279,0.0005</t>
-  </si>
-  <si>
-    <t>0.3827,0.0025,0.7484,0.0003</t>
-  </si>
-  <si>
-    <t>0.0646,0.0653,0.8644,0.0001</t>
-  </si>
-  <si>
-    <t>0.0458,0.8335,0.0550,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.0007,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.8742,0.0441,0.0240,0.0011</t>
-  </si>
-  <si>
-    <t>0.0176,0.9686,0.0015,0.0022</t>
-  </si>
-  <si>
-    <t>0.0560,0.8546,0.0420,0.0004</t>
-  </si>
-  <si>
-    <t>0.0736,0.8939,0.0092,0.0007</t>
-  </si>
-  <si>
-    <t>0.0014,0.0010,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0003,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0790,0.0007,0.9452,0.0002</t>
-  </si>
-  <si>
-    <t>0.3721,0.0003,0.8035,0.0001</t>
-  </si>
-  <si>
-    <t>0.0035,0.0003,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0739,0.0027,0.9493,0.0001</t>
-  </si>
-  <si>
-    <t>0.9283,0.0731,0.0066,0.0003</t>
-  </si>
-  <si>
-    <t>0.9587,0.0264,0.0082,0.0005</t>
-  </si>
-  <si>
-    <t>0.8850,0.1172,0.0071,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.9876,0.0074,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9614,0.0325,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.7195,0.3259,0.0114,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.1642,0.9940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0480,0.0010,0.9695,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.3328,0.9724,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.1169,0.7721,0.0424,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.9985,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.5933,0.0093,0.4691,0.0015</t>
-  </si>
-  <si>
-    <t>0.6898,0.0216,0.3111,0.0007</t>
-  </si>
-  <si>
-    <t>0.0041,0.0025,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.5031,0.9829,0.0000</t>
-  </si>
-  <si>
-    <t>0.0181,0.1191,0.9128,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9850,0.1066,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.8097,0.8390,0.0000</t>
-  </si>
-  <si>
-    <t>0.7175,0.0014,0.1416,0.0263</t>
-  </si>
-  <si>
-    <t>0.3544,0.0003,0.0015,0.7434</t>
-  </si>
-  <si>
-    <t>0.8935,0.0006,0.0054,0.0286</t>
-  </si>
-  <si>
-    <t>0.8701,0.0003,0.0113,0.0356</t>
-  </si>
-  <si>
-    <t>0.9373,0.0009,0.0172,0.0060</t>
-  </si>
-  <si>
-    <t>0.8738,0.0006,0.0058,0.0325</t>
-  </si>
-  <si>
-    <t>0.0041,0.7823,0.7049,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.4812,0.9455,0.0000</t>
-  </si>
-  <si>
-    <t>0.0078,0.2362,0.9276,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.1335,0.9808,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.4480,0.9789,0.0000</t>
-  </si>
-  <si>
-    <t>0.1119,0.1666,0.5180,0.0001</t>
-  </si>
-  <si>
-    <t>0.9868,0.0100,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9834,0.0139,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9664,0.0380,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9671,0.0180,0.0019,0.0013</t>
-  </si>
-  <si>
-    <t>0.9214,0.0785,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9851,0.0102,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9700,0.0264,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.9575,0.0512,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0017,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9910,0.0059,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9903,0.0063,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9957,0.0022,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9873,0.0078,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9697,0.0294,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9781,0.0180,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9946,0.0032,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.1180,0.0006,0.9320,0.0001</t>
-  </si>
-  <si>
-    <t>0.8762,0.0076,0.1284,0.0003</t>
-  </si>
-  <si>
-    <t>0.0776,0.0013,0.9505,0.0001</t>
-  </si>
-  <si>
-    <t>0.0178,0.9720,0.0040,0.0003</t>
-  </si>
-  <si>
-    <t>0.0246,0.9627,0.0058,0.0004</t>
-  </si>
-  <si>
-    <t>0.0208,0.9717,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.0609,0.9306,0.0043,0.0006</t>
-  </si>
-  <si>
-    <t>0.0407,0.9473,0.0043,0.0005</t>
-  </si>
-  <si>
-    <t>0.0037,0.9913,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.4672,0.5475,0.0181,0.0006</t>
-  </si>
-  <si>
-    <t>0.8609,0.0064,0.1622,0.0003</t>
-  </si>
-  <si>
-    <t>0.2860,0.0010,0.8280,0.0001</t>
-  </si>
-  <si>
-    <t>0.9108,0.0035,0.0914,0.0003</t>
-  </si>
-  <si>
-    <t>0.7028,0.0136,0.3506,0.0005</t>
-  </si>
-  <si>
-    <t>0.6528,0.1073,0.0487,0.0218</t>
-  </si>
-  <si>
-    <t>0.0015,0.9949,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.0028,0.9934,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.4373,0.3544,0.0514,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9627,0.6360,0.0001</t>
-  </si>
-  <si>
-    <t>0.2242,0.7688,0.0152,0.0002</t>
-  </si>
-  <si>
-    <t>0.4989,0.5945,0.0070,0.0002</t>
-  </si>
-  <si>
-    <t>0.6137,0.4339,0.0131,0.0006</t>
-  </si>
-  <si>
-    <t>0.8943,0.0971,0.0104,0.0004</t>
-  </si>
-  <si>
-    <t>0.9436,0.0416,0.0092,0.0004</t>
-  </si>
-  <si>
-    <t>0.9753,0.0183,0.0026,0.0004</t>
-  </si>
-  <si>
-    <t>0.9814,0.0114,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.9926,0.0037,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9692,0.0217,0.0066,0.0003</t>
-  </si>
-  <si>
-    <t>0.9748,0.0205,0.0031,0.0003</t>
-  </si>
-  <si>
-    <t>0.9704,0.0243,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.0292,0.1264,0.8684,0.0001</t>
-  </si>
-  <si>
-    <t>0.0190,0.1397,0.8747,0.0001</t>
-  </si>
-  <si>
-    <t>0.0504,0.0172,0.9334,0.0001</t>
-  </si>
-  <si>
-    <t>0.1560,0.0010,0.9054,0.0001</t>
-  </si>
-  <si>
-    <t>0.9325,0.0048,0.0531,0.0001</t>
-  </si>
-  <si>
-    <t>0.7510,0.0071,0.3335,0.0003</t>
-  </si>
-  <si>
-    <t>0.6899,0.0006,0.5021,0.0002</t>
-  </si>
-  <si>
-    <t>0.8689,0.0116,0.1127,0.0003</t>
-  </si>
-  <si>
-    <t>0.9626,0.0006,0.0039,0.0055</t>
-  </si>
-  <si>
-    <t>0.0070,0.0002,0.0007,0.9960</t>
-  </si>
-  <si>
-    <t>0.4581,0.0014,0.0030,0.5209</t>
-  </si>
-  <si>
-    <t>0.7304,0.0003,0.0130,0.1475</t>
-  </si>
-  <si>
-    <t>0.0012,0.8237,0.7772,0.0000</t>
-  </si>
-  <si>
-    <t>0.9808,0.0133,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.6059,0.3590,0.0220,0.0007</t>
-  </si>
-  <si>
-    <t>0.9686,0.0172,0.0050,0.0003</t>
-  </si>
-  <si>
-    <t>0.4464,0.6108,0.0149,0.0003</t>
-  </si>
-  <si>
-    <t>0.9798,0.0060,0.0045,0.0006</t>
-  </si>
-  <si>
-    <t>0.8998,0.0025,0.0200,0.0132</t>
-  </si>
-  <si>
-    <t>0.9804,0.0095,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.0023,0.0054,0.9946,0.0014</t>
-  </si>
-  <si>
-    <t>0.9623,0.0036,0.0122,0.0014</t>
-  </si>
-  <si>
-    <t>0.9891,0.0027,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.7473,0.1150,0.0631,0.0002</t>
-  </si>
-  <si>
-    <t>0.9237,0.0275,0.0152,0.0012</t>
-  </si>
-  <si>
-    <t>0.9208,0.0272,0.0280,0.0006</t>
-  </si>
-  <si>
-    <t>0.8160,0.0322,0.1128,0.0004</t>
-  </si>
-  <si>
-    <t>0.8932,0.0278,0.0460,0.0004</t>
-  </si>
-  <si>
-    <t>0.8543,0.0372,0.0617,0.0006</t>
-  </si>
-  <si>
-    <t>0.9868,0.0084,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9946,0.0032,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9663,0.0236,0.0035,0.0004</t>
-  </si>
-  <si>
-    <t>0.9892,0.0047,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9891,0.0067,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9820,0.0147,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9868,0.0078,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9816,0.0121,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.6401,0.4200,0.0099,0.0004</t>
-  </si>
-  <si>
-    <t>0.6919,0.3322,0.0127,0.0002</t>
-  </si>
-  <si>
-    <t>0.6512,0.3222,0.0244,0.0004</t>
-  </si>
-  <si>
-    <t>0.1714,0.0157,0.8168,0.0033</t>
-  </si>
-  <si>
-    <t>0.8604,0.1522,0.0067,0.0003</t>
-  </si>
-  <si>
-    <t>0.9198,0.0554,0.0099,0.0006</t>
-  </si>
-  <si>
-    <t>0.8681,0.1322,0.0106,0.0005</t>
-  </si>
-  <si>
-    <t>0.6682,0.3359,0.0210,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.0019,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.8526,0.1108,0.0237,0.0015</t>
-  </si>
-  <si>
-    <t>0.0017,0.0005,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0080,0.0047,0.9919,0.0000</t>
-  </si>
-  <si>
-    <t>0.2012,0.0009,0.8728,0.0002</t>
-  </si>
-  <si>
-    <t>0.0072,0.0014,0.9948,0.0000</t>
-  </si>
-  <si>
-    <t>0.0167,0.0007,0.9875,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.0002,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0070,0.0003,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.6560,0.0071,0.4409,0.0005</t>
-  </si>
-  <si>
-    <t>0.3494,0.0083,0.6980,0.0010</t>
-  </si>
-  <si>
-    <t>0.8364,0.0136,0.1544,0.0004</t>
-  </si>
-  <si>
-    <t>0.8066,0.0131,0.1920,0.0003</t>
-  </si>
-  <si>
-    <t>0.7207,0.0217,0.2473,0.0003</t>
-  </si>
-  <si>
-    <t>0.7522,0.0040,0.3533,0.0003</t>
-  </si>
-  <si>
-    <t>0.8719,0.0030,0.1640,0.0004</t>
-  </si>
-  <si>
-    <t>0.8215,0.0076,0.2189,0.0005</t>
-  </si>
-  <si>
-    <t>0.3142,0.7121,0.0134,0.0007</t>
-  </si>
-  <si>
-    <t>0.0681,0.9237,0.0057,0.0005</t>
-  </si>
-  <si>
-    <t>0.5733,0.4884,0.0187,0.0005</t>
-  </si>
-  <si>
-    <t>0.3684,0.6752,0.0054,0.0013</t>
-  </si>
-  <si>
-    <t>0.0760,0.9156,0.0036,0.0019</t>
-  </si>
-  <si>
-    <t>0.8836,0.0054,0.1321,0.0002</t>
-  </si>
-  <si>
-    <t>0.8840,0.0022,0.1579,0.0003</t>
-  </si>
-  <si>
-    <t>0.8900,0.0030,0.1193,0.0005</t>
-  </si>
-  <si>
-    <t>0.8425,0.0036,0.2249,0.0003</t>
-  </si>
-  <si>
-    <t>0.8274,0.0034,0.2454,0.0003</t>
-  </si>
-  <si>
-    <t>0.0596,0.0007,0.9639,0.0002</t>
-  </si>
-  <si>
-    <t>0.1292,0.0045,0.8981,0.0003</t>
-  </si>
-  <si>
-    <t>0.2481,0.0337,0.7026,0.0012</t>
-  </si>
-  <si>
-    <t>0.1261,0.0006,0.9340,0.0001</t>
-  </si>
-  <si>
-    <t>0.1396,0.0071,0.8777,0.0003</t>
-  </si>
-  <si>
-    <t>0.9841,0.0113,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9487,0.0494,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.9630,0.0317,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9559,0.0456,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.9539,0.0359,0.0028,0.0006</t>
-  </si>
-  <si>
-    <t>0.9804,0.0142,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9463,0.0411,0.0066,0.0007</t>
-  </si>
-  <si>
-    <t>0.9901,0.0072,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0606,0.0023,0.9491,0.0011</t>
-  </si>
-  <si>
-    <t>0.4805,0.0203,0.5285,0.0016</t>
-  </si>
-  <si>
-    <t>0.8691,0.0447,0.0566,0.0014</t>
-  </si>
-  <si>
-    <t>0.0247,0.0003,0.9903,0.0000</t>
-  </si>
-  <si>
-    <t>0.0229,0.0056,0.9803,0.0000</t>
-  </si>
-  <si>
-    <t>0.2129,0.0025,0.8654,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.4610,0.0026,0.6623,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0742,0.0076,0.9306,0.0002</t>
-  </si>
-  <si>
-    <t>0.0148,0.0025,0.9872,0.0001</t>
-  </si>
-  <si>
-    <t>0.8115,0.0012,0.2566,0.0006</t>
-  </si>
-  <si>
-    <t>0.8351,0.0034,0.2494,0.0002</t>
-  </si>
-  <si>
-    <t>0.9375,0.0020,0.0779,0.0001</t>
-  </si>
-  <si>
-    <t>0.9462,0.0424,0.0031,0.0007</t>
-  </si>
-  <si>
-    <t>0.9704,0.0227,0.0025,0.0003</t>
-  </si>
-  <si>
-    <t>0.9917,0.0058,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9544,0.0413,0.0050,0.0005</t>
-  </si>
-  <si>
-    <t>0.8985,0.0779,0.0049,0.0017</t>
-  </si>
-  <si>
-    <t>0.9323,0.0791,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.9744,0.0202,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9510,0.0401,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.3256,0.0028,0.7642,0.0003</t>
-  </si>
-  <si>
-    <t>0.0090,0.0049,0.9910,0.0000</t>
-  </si>
-  <si>
-    <t>0.0263,0.0220,0.9592,0.0001</t>
-  </si>
-  <si>
-    <t>0.5873,0.0176,0.4401,0.0004</t>
-  </si>
-  <si>
-    <t>0.0084,0.0004,0.9951,0.0000</t>
-  </si>
-  <si>
-    <t>0.5130,0.0017,0.6153,0.0007</t>
-  </si>
-  <si>
-    <t>0.5978,0.0015,0.5697,0.0003</t>
-  </si>
-  <si>
-    <t>0.1382,0.0013,0.8968,0.0005</t>
-  </si>
-  <si>
-    <t>0.9793,0.0028,0.0069,0.0006</t>
-  </si>
-  <si>
-    <t>0.8419,0.0032,0.0085,0.0376</t>
-  </si>
-  <si>
-    <t>0.9815,0.0005,0.0037,0.0009</t>
-  </si>
-  <si>
-    <t>0.5900,0.0002,0.0121,0.3325</t>
-  </si>
-  <si>
-    <t>0.1112,0.0003,0.0013,0.9477</t>
-  </si>
-  <si>
-    <t>0.9354,0.0048,0.0459,0.0005</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.8915,0.0338,0.0347,0.0007</t>
+  </si>
+  <si>
+    <t>0.7485,0.0011,0.0045,0.1489</t>
+  </si>
+  <si>
+    <t>0.9606,0.0092,0.0117,0.0008</t>
+  </si>
+  <si>
+    <t>0.9048,0.0021,0.0200,0.0116</t>
+  </si>
+  <si>
+    <t>0.9950,0.0027,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9865,0.0092,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9841,0.0161,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9917,0.0058,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9873,0.0098,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9763,0.0194,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9927,0.0047,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9953,0.0029,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8427,0.0049,0.2122,0.0002</t>
+  </si>
+  <si>
+    <t>0.4011,0.0025,0.7146,0.0003</t>
+  </si>
+  <si>
+    <t>0.6274,0.0050,0.4997,0.0002</t>
+  </si>
+  <si>
+    <t>0.4844,0.0008,0.6787,0.0003</t>
+  </si>
+  <si>
+    <t>0.7108,0.0097,0.3481,0.0006</t>
+  </si>
+  <si>
+    <t>0.0038,0.9927,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0184,0.9732,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.1937,0.7887,0.0193,0.0009</t>
+  </si>
+  <si>
+    <t>0.0695,0.9222,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.0040,0.9917,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.8204,0.0013,0.2874,0.0003</t>
+  </si>
+  <si>
+    <t>0.5939,0.0021,0.5642,0.0003</t>
+  </si>
+  <si>
+    <t>0.0126,0.0003,0.9925,0.0000</t>
+  </si>
+  <si>
+    <t>0.4579,0.0012,0.6962,0.0003</t>
+  </si>
+  <si>
+    <t>0.0354,0.0002,0.9797,0.0001</t>
+  </si>
+  <si>
+    <t>0.3504,0.0005,0.7864,0.0002</t>
+  </si>
+  <si>
+    <t>0.0268,0.0003,0.9851,0.0001</t>
+  </si>
+  <si>
+    <t>0.3866,0.4834,0.0310,0.0005</t>
+  </si>
+  <si>
+    <t>0.8025,0.0763,0.0745,0.0014</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.1908,0.1169,0.6174,0.0009</t>
+  </si>
+  <si>
+    <t>0.9076,0.0429,0.0269,0.0006</t>
+  </si>
+  <si>
+    <t>0.9288,0.0223,0.0291,0.0002</t>
+  </si>
+  <si>
+    <t>0.5188,0.5045,0.0174,0.0010</t>
+  </si>
+  <si>
+    <t>0.1694,0.7287,0.0589,0.0011</t>
+  </si>
+  <si>
+    <t>0.0958,0.1046,0.6439,0.0002</t>
+  </si>
+  <si>
+    <t>0.0819,0.0073,0.9325,0.0001</t>
+  </si>
+  <si>
+    <t>0.0967,0.0018,0.9180,0.0004</t>
+  </si>
+  <si>
+    <t>0.2268,0.0008,0.8462,0.0004</t>
+  </si>
+  <si>
+    <t>0.0560,0.0669,0.8755,0.0001</t>
+  </si>
+  <si>
+    <t>0.0300,0.8833,0.0422,0.0001</t>
+  </si>
+  <si>
+    <t>0.0066,0.0008,0.9939,0.0001</t>
+  </si>
+  <si>
+    <t>0.9146,0.0169,0.0346,0.0009</t>
+  </si>
+  <si>
+    <t>0.0816,0.8698,0.0050,0.0008</t>
+  </si>
+  <si>
+    <t>0.0304,0.9011,0.0495,0.0006</t>
+  </si>
+  <si>
+    <t>0.0678,0.8818,0.0206,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.0008,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0012,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.1010,0.0004,0.9396,0.0002</t>
+  </si>
+  <si>
+    <t>0.3683,0.0003,0.8081,0.0001</t>
+  </si>
+  <si>
+    <t>0.0146,0.0001,0.9928,0.0000</t>
+  </si>
+  <si>
+    <t>0.0453,0.0058,0.9587,0.0001</t>
+  </si>
+  <si>
+    <t>0.9344,0.0647,0.0065,0.0002</t>
+  </si>
+  <si>
+    <t>0.9597,0.0248,0.0079,0.0003</t>
+  </si>
+  <si>
+    <t>0.8931,0.1180,0.0086,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9726,0.0205,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.9596,0.0335,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.6114,0.4149,0.0160,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.4302,0.9915,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0030,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0446,0.0011,0.9727,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.2744,0.9091,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.0003,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.1009,0.8666,0.0133,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.9967,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.8741,0.0226,0.0918,0.0006</t>
+  </si>
+  <si>
+    <t>0.7277,0.0134,0.3072,0.0005</t>
+  </si>
+  <si>
+    <t>0.0076,0.0045,0.9919,0.0004</t>
+  </si>
+  <si>
+    <t>0.0062,0.4216,0.8757,0.0001</t>
+  </si>
+  <si>
+    <t>0.0153,0.2165,0.8524,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9837,0.4646,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.8003,0.8019,0.0000</t>
+  </si>
+  <si>
+    <t>0.6848,0.0003,0.0302,0.1295</t>
+  </si>
+  <si>
+    <t>0.2103,0.0015,0.0045,0.8332</t>
+  </si>
+  <si>
+    <t>0.7254,0.0002,0.0016,0.2549</t>
+  </si>
+  <si>
+    <t>0.8910,0.0007,0.0158,0.0210</t>
+  </si>
+  <si>
+    <t>0.9160,0.0016,0.0232,0.0100</t>
+  </si>
+  <si>
+    <t>0.9021,0.0010,0.0075,0.0182</t>
+  </si>
+  <si>
+    <t>0.0138,0.4746,0.7181,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.2292,0.9576,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.4884,0.9836,0.0000</t>
+  </si>
+  <si>
+    <t>0.0115,0.0538,0.9677,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.4981,0.9494,0.0000</t>
+  </si>
+  <si>
+    <t>0.0519,0.2356,0.5944,0.0001</t>
+  </si>
+  <si>
+    <t>0.9883,0.0104,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9754,0.0257,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9530,0.0607,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9817,0.0124,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9005,0.0878,0.0026,0.0007</t>
+  </si>
+  <si>
+    <t>0.9776,0.0192,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9713,0.0211,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.9148,0.0963,0.0072,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9827,0.0139,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0038,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9876,0.0101,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9380,0.0602,0.0048,0.0004</t>
+  </si>
+  <si>
+    <t>0.9756,0.0219,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9939,0.0037,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0002,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.4796,0.0009,0.6948,0.0002</t>
+  </si>
+  <si>
+    <t>0.9021,0.0056,0.1030,0.0001</t>
+  </si>
+  <si>
+    <t>0.2016,0.0012,0.8809,0.0001</t>
+  </si>
+  <si>
+    <t>0.0300,0.9581,0.0045,0.0006</t>
+  </si>
+  <si>
+    <t>0.0407,0.9504,0.0046,0.0002</t>
+  </si>
+  <si>
+    <t>0.0406,0.9499,0.0027,0.0009</t>
+  </si>
+  <si>
+    <t>0.0990,0.8871,0.0076,0.0012</t>
+  </si>
+  <si>
+    <t>0.0527,0.9321,0.0070,0.0005</t>
+  </si>
+  <si>
+    <t>0.0088,0.9838,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.5081,0.5127,0.0148,0.0005</t>
+  </si>
+  <si>
+    <t>0.8720,0.0047,0.1553,0.0003</t>
+  </si>
+  <si>
+    <t>0.2206,0.0006,0.8686,0.0001</t>
+  </si>
+  <si>
+    <t>0.8705,0.0042,0.1705,0.0002</t>
+  </si>
+  <si>
+    <t>0.7654,0.0056,0.3229,0.0004</t>
+  </si>
+  <si>
+    <t>0.7286,0.0630,0.1463,0.0035</t>
+  </si>
+  <si>
+    <t>0.0013,0.9961,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.9954,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.3552,0.4577,0.0491,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.9697,0.2976,0.0000</t>
+  </si>
+  <si>
+    <t>0.1377,0.8203,0.0240,0.0004</t>
+  </si>
+  <si>
+    <t>0.6153,0.4255,0.0158,0.0004</t>
+  </si>
+  <si>
+    <t>0.6717,0.3495,0.0157,0.0005</t>
+  </si>
+  <si>
+    <t>0.9709,0.0222,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0037,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9771,0.0149,0.0028,0.0004</t>
+  </si>
+  <si>
+    <t>0.9612,0.0330,0.0060,0.0003</t>
+  </si>
+  <si>
+    <t>0.9857,0.0099,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9652,0.0200,0.0092,0.0004</t>
+  </si>
+  <si>
+    <t>0.9560,0.0336,0.0060,0.0006</t>
+  </si>
+  <si>
+    <t>0.9831,0.0095,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.0054,0.3005,0.9290,0.0001</t>
+  </si>
+  <si>
+    <t>0.0092,0.1247,0.9371,0.0000</t>
+  </si>
+  <si>
+    <t>0.1190,0.0085,0.8852,0.0001</t>
+  </si>
+  <si>
+    <t>0.1015,0.0061,0.9127,0.0001</t>
+  </si>
+  <si>
+    <t>0.9383,0.0036,0.0539,0.0001</t>
+  </si>
+  <si>
+    <t>0.6616,0.0034,0.4731,0.0004</t>
+  </si>
+  <si>
+    <t>0.6299,0.0008,0.5715,0.0001</t>
+  </si>
+  <si>
+    <t>0.8718,0.0189,0.0640,0.0004</t>
+  </si>
+  <si>
+    <t>0.9537,0.0007,0.0070,0.0055</t>
+  </si>
+  <si>
+    <t>0.0251,0.0003,0.0010,0.9865</t>
+  </si>
+  <si>
+    <t>0.3395,0.0033,0.0039,0.6543</t>
+  </si>
+  <si>
+    <t>0.7204,0.0003,0.0094,0.1635</t>
+  </si>
+  <si>
+    <t>0.0026,0.6984,0.7942,0.0000</t>
+  </si>
+  <si>
+    <t>0.9809,0.0105,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.6697,0.2693,0.0279,0.0006</t>
+  </si>
+  <si>
+    <t>0.9661,0.0170,0.0059,0.0003</t>
+  </si>
+  <si>
+    <t>0.4894,0.5663,0.0126,0.0004</t>
+  </si>
+  <si>
+    <t>0.9739,0.0099,0.0056,0.0005</t>
+  </si>
+  <si>
+    <t>0.9423,0.0017,0.0161,0.0041</t>
+  </si>
+  <si>
+    <t>0.9882,0.0045,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0009,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.9688,0.0033,0.0129,0.0007</t>
+  </si>
+  <si>
+    <t>0.9857,0.0032,0.0037,0.0004</t>
+  </si>
+  <si>
+    <t>0.8259,0.0872,0.0316,0.0002</t>
+  </si>
+  <si>
+    <t>0.8837,0.0621,0.0167,0.0009</t>
+  </si>
+  <si>
+    <t>0.9339,0.0273,0.0179,0.0006</t>
+  </si>
+  <si>
+    <t>0.7366,0.0668,0.1223,0.0009</t>
+  </si>
+  <si>
+    <t>0.8377,0.0305,0.1037,0.0005</t>
+  </si>
+  <si>
+    <t>0.8145,0.0658,0.0625,0.0006</t>
+  </si>
+  <si>
+    <t>0.9894,0.0065,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9949,0.0031,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9812,0.0139,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.9928,0.0033,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9911,0.0054,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9800,0.0183,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9854,0.0079,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9555,0.0341,0.0046,0.0005</t>
+  </si>
+  <si>
+    <t>0.6485,0.4007,0.0117,0.0004</t>
+  </si>
+  <si>
+    <t>0.6582,0.3714,0.0157,0.0002</t>
+  </si>
+  <si>
+    <t>0.7240,0.2400,0.0220,0.0003</t>
+  </si>
+  <si>
+    <t>0.3002,0.0935,0.5647,0.0024</t>
+  </si>
+  <si>
+    <t>0.7059,0.3584,0.0063,0.0003</t>
+  </si>
+  <si>
+    <t>0.8934,0.0874,0.0125,0.0006</t>
+  </si>
+  <si>
+    <t>0.8106,0.1903,0.0150,0.0007</t>
+  </si>
+  <si>
+    <t>0.7953,0.2003,0.0215,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.8864,0.0738,0.0248,0.0010</t>
+  </si>
+  <si>
+    <t>0.0021,0.0012,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0260,0.0035,0.9759,0.0001</t>
+  </si>
+  <si>
+    <t>0.1518,0.0006,0.9094,0.0002</t>
+  </si>
+  <si>
+    <t>0.0056,0.0018,0.9958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0058,0.0010,0.9957,0.0000</t>
+  </si>
+  <si>
+    <t>0.0188,0.0002,0.9916,0.0000</t>
+  </si>
+  <si>
+    <t>0.0261,0.0002,0.9853,0.0001</t>
+  </si>
+  <si>
+    <t>0.6269,0.0094,0.4486,0.0008</t>
+  </si>
+  <si>
+    <t>0.1337,0.0031,0.8897,0.0005</t>
+  </si>
+  <si>
+    <t>0.8375,0.0073,0.1945,0.0003</t>
+  </si>
+  <si>
+    <t>0.7738,0.0128,0.2314,0.0002</t>
+  </si>
+  <si>
+    <t>0.7471,0.0147,0.2649,0.0002</t>
+  </si>
+  <si>
+    <t>0.7819,0.0042,0.3160,0.0003</t>
+  </si>
+  <si>
+    <t>0.8667,0.0062,0.1378,0.0006</t>
+  </si>
+  <si>
+    <t>0.6737,0.0029,0.4503,0.0006</t>
+  </si>
+  <si>
+    <t>0.2729,0.7565,0.0108,0.0003</t>
+  </si>
+  <si>
+    <t>0.1657,0.8503,0.0066,0.0003</t>
+  </si>
+  <si>
+    <t>0.8249,0.2032,0.0123,0.0003</t>
+  </si>
+  <si>
+    <t>0.0962,0.8977,0.0036,0.0025</t>
+  </si>
+  <si>
+    <t>0.1270,0.8703,0.0056,0.0022</t>
+  </si>
+  <si>
+    <t>0.9382,0.0054,0.0371,0.0001</t>
+  </si>
+  <si>
+    <t>0.8893,0.0027,0.1375,0.0003</t>
+  </si>
+  <si>
+    <t>0.9152,0.0046,0.0850,0.0002</t>
+  </si>
+  <si>
+    <t>0.8467,0.0054,0.2014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9062,0.0024,0.1245,0.0002</t>
+  </si>
+  <si>
+    <t>0.2517,0.0013,0.8511,0.0002</t>
+  </si>
+  <si>
+    <t>0.0572,0.0021,0.9524,0.0002</t>
+  </si>
+  <si>
+    <t>0.2551,0.0086,0.7960,0.0004</t>
+  </si>
+  <si>
+    <t>0.1350,0.0011,0.9207,0.0001</t>
+  </si>
+  <si>
+    <t>0.1161,0.0052,0.8974,0.0003</t>
+  </si>
+  <si>
+    <t>0.9764,0.0201,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9163,0.0906,0.0047,0.0004</t>
+  </si>
+  <si>
+    <t>0.9431,0.0542,0.0029,0.0005</t>
+  </si>
+  <si>
+    <t>0.9539,0.0490,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.9674,0.0272,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9605,0.0383,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.9248,0.0752,0.0067,0.0003</t>
+  </si>
+  <si>
+    <t>0.9856,0.0113,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.0429,0.0014,0.9624,0.0013</t>
+  </si>
+  <si>
+    <t>0.4346,0.0597,0.4717,0.0024</t>
+  </si>
+  <si>
+    <t>0.9055,0.0322,0.0452,0.0006</t>
+  </si>
+  <si>
+    <t>0.0498,0.0008,0.9769,0.0000</t>
+  </si>
+  <si>
+    <t>0.0213,0.0014,0.9880,0.0000</t>
+  </si>
+  <si>
+    <t>0.0434,0.0024,0.9725,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.0001,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.1155,0.0035,0.9124,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1007,0.0098,0.9017,0.0003</t>
+  </si>
+  <si>
+    <t>0.0191,0.0028,0.9828,0.0001</t>
+  </si>
+  <si>
+    <t>0.7970,0.0008,0.2714,0.0006</t>
+  </si>
+  <si>
+    <t>0.8526,0.0013,0.2375,0.0002</t>
+  </si>
+  <si>
+    <t>0.9093,0.0011,0.1150,0.0002</t>
+  </si>
+  <si>
+    <t>0.8333,0.1809,0.0067,0.0007</t>
+  </si>
+  <si>
+    <t>0.9526,0.0486,0.0039,0.0003</t>
+  </si>
+  <si>
+    <t>0.9919,0.0051,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9076,0.0928,0.0108,0.0008</t>
+  </si>
+  <si>
+    <t>0.9702,0.0138,0.0027,0.0014</t>
+  </si>
+  <si>
+    <t>0.9584,0.0369,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.9706,0.0255,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9488,0.0385,0.0037,0.0010</t>
+  </si>
+  <si>
+    <t>0.1483,0.0033,0.8795,0.0003</t>
+  </si>
+  <si>
+    <t>0.0729,0.0066,0.9274,0.0001</t>
+  </si>
+  <si>
+    <t>0.0252,0.0486,0.9284,0.0001</t>
+  </si>
+  <si>
+    <t>0.4075,0.0072,0.6769,0.0004</t>
+  </si>
+  <si>
+    <t>0.0391,0.0015,0.9747,0.0001</t>
+  </si>
+  <si>
+    <t>0.4233,0.0015,0.6819,0.0009</t>
+  </si>
+  <si>
+    <t>0.7532,0.0033,0.3730,0.0003</t>
+  </si>
+  <si>
+    <t>0.2272,0.0006,0.8662,0.0002</t>
+  </si>
+  <si>
+    <t>0.9755,0.0035,0.0062,0.0009</t>
+  </si>
+  <si>
+    <t>0.8705,0.0024,0.0093,0.0255</t>
+  </si>
+  <si>
+    <t>0.9817,0.0006,0.0031,0.0015</t>
+  </si>
+  <si>
+    <t>0.5628,0.0003,0.0048,0.4614</t>
+  </si>
+  <si>
+    <t>0.0727,0.0003,0.0009,0.9686</t>
+  </si>
+  <si>
+    <t>0.9469,0.0076,0.0270,0.0004</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>259</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2581,7 @@
         <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2956,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>259</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>259</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>259</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>259</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>259</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3096,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>261</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3617,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3656,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3670,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4065,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4387,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4401,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4639,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4653,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4765,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5378,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5420,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>259</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>259</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>259</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
